--- a/Luban/Config/Datas/Levels/L07/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L07/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L7 W1/25; N=37; EHP=213.268000; normal:17x18,normal:18x19</t>
+          <t>L7 W1/25; N=37; EHP=419.859833; normal:17x18,normal:18x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L7 W2/25; N=43; EHP=259.525829; normal:17x22,normal:18x21</t>
+          <t>L7 W2/25; N=43; EHP=510.927431; normal:17x22,normal:18x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3344136,3344673,3344019,3344136,3344673,3344091,3344136,3344673,3344099,3344136,3344673,3344099,3344136,3344673,3344107,3344136,3344673,3344115,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344136,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144</t>
+          <t>3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344136,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344144,3344136,3344136,3344136,3344136,3344136,3344136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L7 W3/25; N=49; EHP=327.173862; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x15,normal:18x15,swarm:84x13</t>
+          <t>L7 W3/25; N=49; EHP=695.759524; normal:17x21,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3346136,3346673,3346019,3346136,3346673,3346019,3346136,3346673,3346091,3346136,3346673,3346099,3346136,3346673,3346107,3346136,3346673,3346107,3346136,3346673,3346115,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346136,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144</t>
+          <t>3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346136,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346144,3346136,3346136,3346136,3346136,3346136,3346136,3346136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L7 W4/25; N=55; EHP=422.872978; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x17,normal:18x16,swarm:84x15</t>
+          <t>L7 W4/25; N=55; EHP=902.337417; normal:17x24,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3348136,3348673,3348019,3348668,3348136,3348673,3348091,3348668,3348136,3348673,3348091,3348668,3348136,3348673,3348099,3348868,3348136,3348673,3348107,3348868,3348136,3348673,3348107,3348868,3348136,3348673,3348115,3348988,3348136,3348673,3348988,3348136,3348673,3348988,3348136,3348673,3348136,3348673,3348136,3348673,3348136,3348673,3348136,3348673,3348144,3348673,3348144,3348673,3348144,3348673,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144</t>
+          <t>3348136,3348019,3348019,3348668,3348136,3348091,3348091,3348668,3348136,3348091,3348091,3348668,3348136,3348099,3348099,3348868,3348136,3348107,3348107,3348868,3348136,3348107,3348107,3348868,3348136,3348115,3348115,3348988,3348136,3348673,3348988,3348136,3348673,3348988,3348136,3348673,3348136,3348673,3348136,3348673,3348136,3348673,3348136,3348673,3348144,3348673,3348144,3348673,3348144,3348673,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144,3348144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L7 W5/25; N=61; EHP=807.794719; air:2x1,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x14,normal:18x14,medium:83x3,swarm:84x17,medium:108x3,medium:123x3</t>
+          <t>L7 W5/25; N=61; EHP=1609.662338; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x3,medium:108x3,medium:123x3,normal:17x14,normal:18x14,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3350136,3350673,3350242,3350019,3350668,3350136,3350673,3350242,3350091,3350668,3350136,3350673,3350242,3350091,3350668,3350136,3350673,3350242,3350099,3350868,3350136,3350673,3350786,3350099,3350868,3350136,3350673,3350786,3350107,3350868,3350136,3350673,3350786,3350115,3350988,3350136,3350673,3350786,3350115,3350988,3350136,3350673,3350988,3350136,3350673,3350988,3350136,3350673,3350136,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350144,3350144,3350144,3350144</t>
+          <t>3350136,3350019,3350242,3350019,3350668,3350136,3350091,3350242,3350091,3350668,3350136,3350091,3350242,3350091,3350668,3350136,3350099,3350242,3350099,3350868,3350136,3350099,3350786,3350099,3350868,3350136,3350107,3350786,3350107,3350868,3350136,3350115,3350786,3350115,3350988,3350136,3350115,3350786,3350115,3350988,3350136,3350673,3350988,3350136,3350673,3350988,3350136,3350673,3350136,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350673,3350144,3350144,3350144,3350144,3350144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L7 W6/25; N=67; EHP=824.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x12,normal:18x11,fast:30x4,medium:83x3,swarm:84x18,fast:98x4,medium:108x3,medium:123x4</t>
+          <t>L7 W6/25; N=67; EHP=1643.103383; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x4,fast:98x4,medium:83x3,medium:108x3,medium:123x4,normal:17x12,normal:18x11,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3352136,3352673,3352242,3352019,3352668,3352136,3352673,3352242,3352019,3352668,3352136,3352673,3352242,3352091,3352668,3352136,3352673,3352242,3352099,3352868,3352136,3352673,3352786,3352099,3352868,3352136,3352673,3352786,3352107,3352868,3352136,3352673,3352786,3352107,3352868,3352136,3352673,3352786,3352115,3352988,3352136,3352673,3352115,3352988,3352136,3352673,3352988,3352136,3352673,3352136,3352673,3352136,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352144,3352144,3352144,3352144,3352144</t>
+          <t>3352136,3352019,3352242,3352019,3352668,3352136,3352019,3352242,3352019,3352668,3352136,3352091,3352242,3352091,3352668,3352136,3352099,3352242,3352099,3352868,3352136,3352099,3352786,3352099,3352868,3352136,3352107,3352786,3352107,3352868,3352136,3352107,3352786,3352107,3352868,3352136,3352115,3352786,3352115,3352988,3352136,3352115,3352115,3352988,3352136,3352673,3352988,3352136,3352673,3352136,3352673,3352136,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352673,3352144,3352144,3352144,3352144,3352144,3352144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L7 W7/25; N=73; EHP=944.885603; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x13,normal:18x13,fast:30x4,medium:83x3,swarm:84x20,fast:98x4,medium:108x4,medium:123x3</t>
+          <t>L7 W7/25; N=73; EHP=1885.236124; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x4,fast:98x4,medium:83x3,medium:108x4,medium:123x3,normal:17x13,normal:18x13,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3354136,3354673,3354242,3354019,3354668,3354136,3354673,3354242,3354019,3354668,3354136,3354673,3354242,3354091,3354668,3354136,3354673,3354242,3354091,3354668,3354136,3354673,3354786,3354099,3354868,3354136,3354673,3354786,3354099,3354868,3354136,3354673,3354786,3354107,3354868,3354136,3354673,3354786,3354107,3354988,3354136,3354673,3354786,3354115,3354988,3354136,3354673,3354988,3354136,3354673,3354988,3354136,3354673,3354136,3354673,3354136,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354144,3354144,3354144,3354144,3354144</t>
+          <t>3354136,3354019,3354242,3354019,3354668,3354136,3354019,3354242,3354019,3354668,3354136,3354091,3354242,3354091,3354668,3354136,3354091,3354242,3354091,3354668,3354136,3354099,3354786,3354099,3354868,3354136,3354099,3354786,3354099,3354868,3354136,3354107,3354786,3354107,3354868,3354136,3354107,3354786,3354107,3354988,3354136,3354115,3354786,3354115,3354988,3354136,3354673,3354988,3354136,3354673,3354988,3354136,3354673,3354136,3354673,3354136,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354673,3354144,3354144,3354144,3354144,3354144,3354144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L7 W8/25; N=79; EHP=1219.397832; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x14,normal:18x14,fast:30x4,medium:83x4,swarm:84x22,fast:98x5,medium:108x3,medium:123x4</t>
+          <t>L7 W8/25; N=79; EHP=2430.342352; air:2x4,air:11x4,air:12x4,air:13x4,air:14x2,fast:30x4,fast:98x5,medium:83x4,medium:108x3,medium:123x4,normal:17x14,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3356136,3356673,3356242,3356019,3356668,3356136,3356673,3356242,3356019,3356668,3356136,3356673,3356242,3356091,3356668,3356136,3356673,3356242,3356091,3356668,3356136,3356673,3356242,3356099,3356868,3356136,3356673,3356786,3356099,3356868,3356136,3356673,3356786,3356107,3356868,3356136,3356673,3356786,3356107,3356868,3356136,3356673,3356786,3356115,3356988,3356136,3356673,3356786,3356115,3356988,3356136,3356673,3356988,3356136,3356673,3356988,3356136,3356673,3356136,3356673,3356136,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356144,3356144,3356144,3356144,3356144,3356144</t>
+          <t>3356136,3356019,3356242,3356019,3356668,3356136,3356019,3356242,3356019,3356668,3356136,3356091,3356242,3356091,3356668,3356136,3356091,3356242,3356091,3356668,3356136,3356099,3356242,3356099,3356868,3356136,3356099,3356786,3356099,3356868,3356136,3356107,3356786,3356107,3356868,3356136,3356107,3356786,3356107,3356868,3356136,3356115,3356786,3356115,3356988,3356136,3356115,3356786,3356115,3356988,3356136,3356673,3356988,3356136,3356673,3356988,3356136,3356673,3356136,3356673,3356136,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356673,3356144,3356144,3356144,3356144,3356144,3356144,3356144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L7 W9/25; N=85; EHP=1557.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x5,medium:83x4,swarm:84x23,fast:98x5,medium:108x4,medium:123x4</t>
+          <t>L7 W9/25; N=85; EHP=3104.382137; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x5,fast:98x5,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3358136,3358673,3358242,3358019,3358668,3358136,3358673,3358242,3358019,3358668,3358136,3358673,3358242,3358091,3358668,3358136,3358673,3358242,3358091,3358668,3358136,3358673,3358242,3358099,3358868,3358136,3358673,3358786,3358099,3358868,3358136,3358673,3358786,3358107,3358868,3358136,3358673,3358786,3358107,3358868,3358136,3358673,3358786,3358107,3358868,3358136,3358673,3358786,3358115,3358988,3358136,3358673,3358115,3358988,3358136,3358673,3358988,3358136,3358673,3358988,3358136,3358673,3358136,3358673,3358136,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358144,3358144,3358144,3358144,3358144,3358144</t>
+          <t>3358136,3358019,3358242,3358019,3358668,3358136,3358019,3358242,3358019,3358668,3358136,3358091,3358242,3358091,3358668,3358136,3358091,3358242,3358091,3358668,3358136,3358099,3358242,3358099,3358868,3358136,3358099,3358786,3358099,3358868,3358136,3358107,3358786,3358107,3358868,3358136,3358107,3358786,3358107,3358868,3358136,3358107,3358786,3358107,3358868,3358136,3358115,3358786,3358115,3358988,3358136,3358115,3358115,3358988,3358136,3358673,3358988,3358136,3358673,3358988,3358136,3358673,3358136,3358673,3358136,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358673,3358144,3358144,3358144,3358144,3358144,3358144,3358144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L7 W10/25; N=91; EHP=2876.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x16,fast:30x5,medium:83x4,swarm:84x25,fast:98x5,medium:108x5,medium:123x4</t>
+          <t>L7 W10/25; N=91; EHP=5736.291152; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x5,fast:98x5,medium:83x4,medium:108x5,medium:123x4,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3360136,3360673,3360242,3360019,3360668,3360253,3360136,3360673,3360242,3360019,3360668,3360253,3360136,3360673,3360242,3360091,3360668,3360325,3360136,3360673,3360242,3360091,3360668,3360325,3360136,3360673,3360466,3360091,3360668,3360645,3360136,3360673,3360466,3360099,3360868,3360645,3360136,3360673,3360466,3360099,3360868,3360693,3360136,3360673,3360786,3360107,3360868,3360709,3360136,3360673,3360786,3360107,3360868,3360709,3360136,3360673,3360786,3360115,3360988,3360136,3360673,3360786,3360115,3360988,3360136,3360673,3360115,3360988,3360144,3360673,3360988,3360144,3360673,3360988,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360673,3360673,3360673</t>
+          <t>3360136,3360019,3360242,3360019,3360668,3360253,3360136,3360019,3360242,3360019,3360668,3360253,3360136,3360091,3360242,3360091,3360668,3360325,3360136,3360091,3360242,3360091,3360668,3360325,3360136,3360091,3360466,3360091,3360668,3360645,3360136,3360099,3360466,3360099,3360868,3360645,3360136,3360099,3360466,3360099,3360868,3360693,3360136,3360107,3360786,3360107,3360868,3360709,3360136,3360107,3360786,3360107,3360868,3360709,3360136,3360115,3360786,3360115,3360988,3360136,3360115,3360786,3360115,3360988,3360136,3360115,3360115,3360988,3360144,3360673,3360988,3360144,3360673,3360988,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360144,3360673,3360673,3360673,3360673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L7 W11/25; N=97; EHP=2934.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x12,normal:18x12,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,heavy:80x2,medium:83x5,swarm:84x27,heavy:86x1,heavy:88x2,fast:98x4,medium:108x4,medium:123x5</t>
+          <t>L7 W11/25; N=97; EHP=5845.536947; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x4,fast:58x3,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x1,heavy:88x2,medium:83x5,medium:108x4,medium:123x5,normal:17x12,normal:18x12,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3362136,3362673,3362242,3362019,3362668,3362253,3362136,3362673,3362242,3362019,3362668,3362253,3362136,3362673,3362242,3362091,3362668,3362325,3362136,3362673,3362242,3362091,3362668,3362325,3362136,3362673,3362466,3362099,3362668,3362645,3362136,3362673,3362466,3362099,3362868,3362645,3362136,3362673,3362466,3362099,3362868,3362693,3362136,3362673,3362466,3362107,3362868,3362693,3362136,3362673,3362786,3362107,3362868,3362709,3362136,3362673,3362786,3362115,3362868,3362709,3362136,3362673,3362786,3362115,3362988,3362136,3362673,3362786,3362115,3362988,3362136,3362673,3362988,3362144,3362673,3362988,3362144,3362673,3362988,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362673,3362673</t>
+          <t>3362136,3362019,3362242,3362019,3362668,3362253,3362136,3362019,3362242,3362019,3362668,3362253,3362136,3362091,3362242,3362091,3362668,3362325,3362136,3362091,3362242,3362091,3362668,3362325,3362136,3362099,3362466,3362099,3362668,3362645,3362136,3362099,3362466,3362099,3362868,3362645,3362136,3362099,3362466,3362099,3362868,3362693,3362136,3362107,3362466,3362107,3362868,3362693,3362136,3362107,3362786,3362107,3362868,3362709,3362136,3362115,3362786,3362115,3362868,3362709,3362136,3362115,3362786,3362115,3362988,3362136,3362115,3362786,3362115,3362988,3362136,3362673,3362988,3362144,3362673,3362988,3362144,3362673,3362988,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362144,3362673,3362673,3362673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L7 W12/25; N=103; EHP=3037.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,heavy:80x2,medium:83x5,swarm:84x28,heavy:86x2,heavy:88x2,fast:98x4,medium:108x5,medium:123x5</t>
+          <t>L7 W12/25; N=103; EHP=6045.795334; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x4,fast:58x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3364136,3364673,3364242,3364019,3364668,3364253,3364136,3364673,3364242,3364019,3364668,3364253,3364136,3364673,3364242,3364019,3364668,3364325,3364136,3364673,3364242,3364091,3364668,3364325,3364136,3364673,3364466,3364091,3364668,3364645,3364136,3364673,3364466,3364099,3364868,3364645,3364136,3364673,3364466,3364099,3364868,3364693,3364136,3364673,3364466,3364099,3364868,3364693,3364136,3364673,3364466,3364107,3364868,3364709,3364136,3364673,3364786,3364107,3364868,3364709,3364136,3364673,3364786,3364107,3364868,3364136,3364673,3364786,3364115,3364988,3364136,3364673,3364786,3364115,3364988,3364144,3364673,3364988,3364144,3364673,3364988,3364144,3364673,3364988,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364673,3364673,3364673</t>
+          <t>3364136,3364019,3364242,3364019,3364668,3364253,3364136,3364019,3364242,3364019,3364668,3364253,3364136,3364019,3364242,3364019,3364668,3364325,3364136,3364091,3364242,3364091,3364668,3364325,3364136,3364091,3364466,3364091,3364668,3364645,3364136,3364099,3364466,3364099,3364868,3364645,3364136,3364099,3364466,3364099,3364868,3364693,3364136,3364099,3364466,3364099,3364868,3364693,3364136,3364107,3364466,3364107,3364868,3364709,3364136,3364107,3364786,3364107,3364868,3364709,3364136,3364107,3364786,3364107,3364868,3364136,3364115,3364786,3364115,3364988,3364136,3364115,3364786,3364115,3364988,3364144,3364673,3364988,3364144,3364673,3364988,3364144,3364673,3364988,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364673,3364673,3364673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L7 W13/25; N=109; EHP=3705.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x13,normal:18x14,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,heavy:80x2,medium:83x5,swarm:84x30,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x5</t>
+          <t>L7 W13/25; N=109; EHP=7378.229823; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x4,fast:58x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,medium:83x5,medium:108x6,medium:123x5,normal:17x13,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3366136,3366673,3366242,3366019,3366668,3366253,3366136,3366673,3366242,3366019,3366668,3366253,3366136,3366673,3366242,3366019,3366668,3366325,3366136,3366673,3366242,3366091,3366668,3366325,3366136,3366673,3366242,3366091,3366668,3366645,3366136,3366673,3366466,3366091,3366668,3366645,3366136,3366673,3366466,3366099,3366868,3366645,3366136,3366673,3366466,3366099,3366868,3366693,3366136,3366673,3366466,3366107,3366868,3366693,3366136,3366673,3366786,3366107,3366868,3366709,3366136,3366673,3366786,3366107,3366868,3366709,3366136,3366673,3366786,3366115,3366988,3366136,3366673,3366786,3366115,3366988,3366136,3366673,3366115,3366988,3366144,3366673,3366988,3366144,3366673,3366988,3366144,3366673,3366988,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366673,3366673,3366673,3366673</t>
+          <t>3366136,3366019,3366242,3366019,3366668,3366253,3366136,3366019,3366242,3366019,3366668,3366253,3366136,3366019,3366242,3366019,3366668,3366325,3366136,3366091,3366242,3366091,3366668,3366325,3366136,3366091,3366242,3366091,3366668,3366645,3366136,3366091,3366466,3366091,3366668,3366645,3366136,3366099,3366466,3366099,3366868,3366645,3366136,3366099,3366466,3366099,3366868,3366693,3366136,3366107,3366466,3366107,3366868,3366693,3366136,3366107,3366786,3366107,3366868,3366709,3366136,3366107,3366786,3366107,3366868,3366709,3366136,3366115,3366786,3366115,3366988,3366136,3366115,3366786,3366115,3366988,3366136,3366115,3366115,3366988,3366144,3366673,3366988,3366144,3366673,3366988,3366144,3366673,3366988,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366144,3366673,3366673,3366673,3366673,3366673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L7 W14/25; N=115; EHP=4472.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,heavy:80x3,medium:83x6,swarm:84x32,heavy:86x2,heavy:88x2,fast:98x4,medium:108x5,medium:123x6</t>
+          <t>L7 W14/25; N=115; EHP=8907.367410; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x5,fast:58x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x3,heavy:86x2,heavy:88x2,medium:83x6,medium:108x5,medium:123x6,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3368136,3368673,3368242,3368019,3368668,3368253,3368326,3368136,3368673,3368242,3368019,3368668,3368253,3368136,3368673,3368242,3368019,3368668,3368253,3368136,3368673,3368242,3368091,3368668,3368325,3368136,3368673,3368466,3368091,3368668,3368325,3368136,3368673,3368466,3368091,3368668,3368645,3368136,3368673,3368466,3368099,3368868,3368645,3368136,3368673,3368466,3368099,3368868,3368693,3368136,3368673,3368466,3368099,3368868,3368693,3368136,3368673,3368786,3368107,3368868,3368693,3368136,3368673,3368786,3368107,3368868,3368709,3368136,3368673,3368786,3368107,3368868,3368709,3368136,3368673,3368786,3368115,3368988,3368136,3368673,3368786,3368115,3368988,3368144,3368673,3368115,3368988,3368144,3368673,3368988,3368144,3368673,3368988,3368144,3368673,3368988,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368673,3368673,3368673,3368673,3368673</t>
+          <t>3368136,3368019,3368242,3368019,3368668,3368253,3368326,3368136,3368019,3368242,3368019,3368668,3368253,3368136,3368019,3368242,3368019,3368668,3368253,3368136,3368091,3368242,3368091,3368668,3368325,3368136,3368091,3368466,3368091,3368668,3368325,3368136,3368091,3368466,3368091,3368668,3368645,3368136,3368099,3368466,3368099,3368868,3368645,3368136,3368099,3368466,3368099,3368868,3368693,3368136,3368099,3368466,3368099,3368868,3368693,3368136,3368107,3368786,3368107,3368868,3368693,3368136,3368107,3368786,3368107,3368868,3368709,3368136,3368107,3368786,3368107,3368868,3368709,3368136,3368115,3368786,3368115,3368988,3368136,3368115,3368786,3368115,3368988,3368144,3368115,3368115,3368988,3368144,3368673,3368988,3368144,3368673,3368988,3368144,3368673,3368988,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368144,3368673,3368673,3368673,3368673,3368673,3368673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L7 W15/25; N=121; EHP=7806.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x4,heavy:31x3,elite:40x1,heavy:40x2,fast:58x5,heavy:80x2,medium:83x6,swarm:84x33,heavy:86x3,heavy:88x2,fast:98x5,medium:108x6,medium:123x6</t>
+          <t>L7 W15/25; N=121; EHP=15545.095487; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:40x1,fast:30x4,fast:58x5,fast:98x5,heavy:31x3,heavy:40x2,heavy:80x2,heavy:86x3,heavy:88x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3370136,3370673,3370242,3370019,3370668,3370253,3370136,3370673,3370242,3370019,3370668,3370253,3370136,3370673,3370242,3370019,3370668,3370253,3370136,3370673,3370242,3370091,3370668,3370325,3370136,3370673,3370242,3370091,3370668,3370325,3370136,3370673,3370466,3370091,3370668,3370325,3370136,3370673,3370466,3370099,3370868,3370645,3370136,3370673,3370466,3370099,3370868,3370645,3370136,3370673,3370466,3370099,3370868,3370693,3370136,3370673,3370466,3370107,3370868,3370693,3370136,3370673,3370786,3370107,3370868,3370709,3370136,3370673,3370786,3370107,3370868,3370709,3370136,3370673,3370786,3370115,3370868,3370136,3370673,3370786,3370115,3370988,3370136,3370673,3370786,3370115,3370988,3370136,3370673,3370988,3370144,3370673,3370988,3370144,3370673,3370988,3370144,3370673,3370988,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370673,3370673,3370673,3370673</t>
+          <t>3370136,3370019,3370242,3370019,3370668,3370253,3370136,3370019,3370242,3370019,3370668,3370253,3370136,3370019,3370242,3370019,3370668,3370253,3370136,3370091,3370242,3370091,3370668,3370325,3370136,3370091,3370242,3370091,3370668,3370325,3370136,3370091,3370466,3370091,3370668,3370325,3370136,3370099,3370466,3370099,3370868,3370645,3370136,3370099,3370466,3370099,3370868,3370645,3370136,3370099,3370466,3370099,3370868,3370693,3370136,3370107,3370466,3370107,3370868,3370693,3370136,3370107,3370786,3370107,3370868,3370709,3370136,3370107,3370786,3370107,3370868,3370709,3370136,3370115,3370786,3370115,3370868,3370136,3370115,3370786,3370115,3370988,3370136,3370115,3370786,3370115,3370988,3370136,3370673,3370988,3370144,3370673,3370988,3370144,3370673,3370988,3370144,3370673,3370988,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370144,3370673,3370673,3370673,3370673,3370673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L7 W16/25; N=127; EHP=7963.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x15,fast:30x5,heavy:31x3,heavy:40x3,fast:58x5,heavy:80x2,medium:83x6,swarm:84x35,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x6</t>
+          <t>L7 W16/25; N=127; EHP=15854.937423; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x5,fast:58x5,fast:98x5,heavy:31x3,heavy:40x3,heavy:80x2,heavy:86x2,heavy:88x2,medium:83x6,medium:108x7,medium:123x6,normal:17x16,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3372136,3372673,3372242,3372019,3372668,3372253,3372136,3372673,3372242,3372019,3372668,3372253,3372136,3372673,3372242,3372019,3372668,3372325,3372136,3372673,3372242,3372091,3372668,3372325,3372136,3372673,3372242,3372091,3372668,3372325,3372136,3372673,3372466,3372091,3372668,3372645,3372136,3372673,3372466,3372099,3372668,3372645,3372136,3372673,3372466,3372099,3372868,3372645,3372136,3372673,3372466,3372099,3372868,3372693,3372136,3372673,3372466,3372107,3372868,3372693,3372136,3372673,3372786,3372107,3372868,3372709,3372136,3372673,3372786,3372107,3372868,3372709,3372136,3372673,3372786,3372115,3372868,3372709,3372136,3372673,3372786,3372115,3372988,3372136,3372673,3372786,3372115,3372988,3372136,3372673,3372115,3372988,3372144,3372673,3372988,3372144,3372673,3372988,3372144,3372673,3372988,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372673,3372673,3372673,3372673</t>
+          <t>3372136,3372019,3372242,3372019,3372668,3372253,3372136,3372019,3372242,3372019,3372668,3372253,3372136,3372019,3372242,3372019,3372668,3372325,3372136,3372091,3372242,3372091,3372668,3372325,3372136,3372091,3372242,3372091,3372668,3372325,3372136,3372091,3372466,3372091,3372668,3372645,3372136,3372099,3372466,3372099,3372668,3372645,3372136,3372099,3372466,3372099,3372868,3372645,3372136,3372099,3372466,3372099,3372868,3372693,3372136,3372107,3372466,3372107,3372868,3372693,3372136,3372107,3372786,3372107,3372868,3372709,3372136,3372107,3372786,3372107,3372868,3372709,3372136,3372115,3372786,3372115,3372868,3372709,3372136,3372115,3372786,3372115,3372988,3372136,3372115,3372786,3372115,3372988,3372136,3372115,3372115,3372988,3372144,3372673,3372988,3372144,3372673,3372988,3372144,3372673,3372988,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372673,3372673,3372673,3372673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L7 W17/25; N=133; EHP=8123.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x16,normal:18x17,fast:30x5,heavy:31x2,heavy:40x3,fast:58x5,heavy:80x3,medium:83x7,swarm:84x37,heavy:86x2,heavy:88x3,fast:98x5,medium:108x6,medium:123x6</t>
+          <t>L7 W17/25; N=133; EHP=16177.262315; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x5,fast:58x5,fast:98x5,heavy:31x2,heavy:40x3,heavy:80x3,heavy:86x2,heavy:88x3,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3374136,3374673,3374242,3374019,3374668,3374253,3374136,3374673,3374242,3374019,3374668,3374253,3374136,3374673,3374242,3374019,3374668,3374325,3374136,3374673,3374242,3374019,3374668,3374325,3374136,3374673,3374242,3374091,3374668,3374645,3374136,3374673,3374466,3374091,3374668,3374645,3374136,3374673,3374466,3374091,3374868,3374645,3374136,3374673,3374466,3374099,3374868,3374693,3374136,3374673,3374466,3374099,3374868,3374693,3374136,3374673,3374466,3374099,3374868,3374693,3374136,3374673,3374786,3374099,3374868,3374709,3374136,3374673,3374786,3374107,3374868,3374709,3374136,3374673,3374786,3374107,3374868,3374709,3374136,3374673,3374786,3374107,3374988,3374136,3374673,3374786,3374115,3374988,3374136,3374673,3374786,3374115,3374988,3374136,3374673,3374115,3374988,3374136,3374673,3374988,3374144,3374673,3374988,3374144,3374673,3374988,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374673,3374673,3374673</t>
+          <t>3374136,3374019,3374242,3374019,3374668,3374253,3374136,3374019,3374242,3374019,3374668,3374253,3374136,3374019,3374242,3374019,3374668,3374325,3374136,3374019,3374242,3374019,3374668,3374325,3374136,3374091,3374242,3374091,3374668,3374645,3374136,3374091,3374466,3374091,3374668,3374645,3374136,3374091,3374466,3374091,3374868,3374645,3374136,3374099,3374466,3374099,3374868,3374693,3374136,3374099,3374466,3374099,3374868,3374693,3374136,3374099,3374466,3374099,3374868,3374693,3374136,3374099,3374786,3374099,3374868,3374709,3374136,3374107,3374786,3374107,3374868,3374709,3374136,3374107,3374786,3374107,3374868,3374709,3374136,3374107,3374786,3374107,3374988,3374136,3374115,3374786,3374115,3374988,3374136,3374115,3374786,3374115,3374988,3374136,3374115,3374115,3374988,3374136,3374673,3374988,3374144,3374673,3374988,3374144,3374673,3374988,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374673,3374673,3374673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L7 W18/25; N=139; EHP=8680.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x18,normal:18x17,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,heavy:80x3,medium:83x6,swarm:84x38,heavy:86x3,heavy:88x3,fast:98x6,medium:108x7,medium:123x7</t>
+          <t>L7 W18/25; N=139; EHP=17290.649306; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x5,fast:58x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x6,medium:108x7,medium:123x7,normal:17x18,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3376136,3376673,3376242,3376019,3376668,3376253,3376136,3376673,3376242,3376019,3376668,3376253,3376136,3376673,3376242,3376019,3376668,3376253,3376136,3376673,3376242,3376019,3376668,3376325,3376136,3376673,3376242,3376091,3376668,3376325,3376136,3376673,3376242,3376091,3376668,3376325,3376136,3376673,3376466,3376091,3376668,3376645,3376136,3376673,3376466,3376099,3376868,3376645,3376136,3376673,3376466,3376099,3376868,3376645,3376136,3376673,3376466,3376099,3376868,3376693,3376136,3376673,3376466,3376107,3376868,3376693,3376136,3376673,3376466,3376107,3376868,3376693,3376136,3376673,3376786,3376107,3376868,3376709,3376136,3376673,3376786,3376107,3376868,3376709,3376136,3376673,3376786,3376115,3376988,3376136,3376673,3376786,3376115,3376988,3376136,3376673,3376786,3376115,3376988,3376136,3376673,3376988,3376144,3376673,3376988,3376144,3376673,3376988,3376144,3376673,3376988,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376673,3376673,3376673,3376673</t>
+          <t>3376136,3376019,3376242,3376019,3376668,3376253,3376136,3376019,3376242,3376019,3376668,3376253,3376136,3376019,3376242,3376019,3376668,3376253,3376136,3376019,3376242,3376019,3376668,3376325,3376136,3376091,3376242,3376091,3376668,3376325,3376136,3376091,3376242,3376091,3376668,3376325,3376136,3376091,3376466,3376091,3376668,3376645,3376136,3376099,3376466,3376099,3376868,3376645,3376136,3376099,3376466,3376099,3376868,3376645,3376136,3376099,3376466,3376099,3376868,3376693,3376136,3376107,3376466,3376107,3376868,3376693,3376136,3376107,3376466,3376107,3376868,3376693,3376136,3376107,3376786,3376107,3376868,3376709,3376136,3376107,3376786,3376107,3376868,3376709,3376136,3376115,3376786,3376115,3376988,3376136,3376115,3376786,3376115,3376988,3376136,3376115,3376786,3376115,3376988,3376136,3376673,3376988,3376144,3376673,3376988,3376144,3376673,3376988,3376144,3376673,3376988,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376144,3376673,3376673,3376673,3376673,3376673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L7 W19/25; N=145; EHP=10052.000000; air:2x4,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x18,normal:18x18,fast:30x6,heavy:31x3,heavy:40x3,fast:58x6,heavy:80x3,medium:83x7,swarm:84x40,heavy:86x3,heavy:88x2,fast:98x5,medium:108x7,medium:123x7</t>
+          <t>L7 W19/25; N=145; EHP=20012.716554; air:2x8,air:11x6,air:12x6,air:13x8,air:14x6,fast:30x6,fast:58x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3378136,3378673,3378242,3378019,3378668,3378253,3378326,3378136,3378673,3378242,3378019,3378668,3378253,3378136,3378673,3378242,3378019,3378668,3378253,3378136,3378673,3378242,3378091,3378668,3378325,3378136,3378673,3378242,3378091,3378668,3378325,3378136,3378673,3378242,3378091,3378668,3378325,3378136,3378673,3378466,3378091,3378668,3378645,3378136,3378673,3378466,3378099,3378668,3378645,3378136,3378673,3378466,3378099,3378868,3378645,3378136,3378673,3378466,3378099,3378868,3378693,3378136,3378673,3378466,3378107,3378868,3378693,3378136,3378673,3378466,3378107,3378868,3378693,3378136,3378673,3378786,3378107,3378868,3378709,3378136,3378673,3378786,3378107,3378868,3378709,3378136,3378673,3378786,3378115,3378868,3378709,3378136,3378673,3378786,3378115,3378988,3378136,3378673,3378786,3378115,3378988,3378136,3378673,3378786,3378115,3378988,3378144,3378673,3378988,3378144,3378673,3378988,3378144,3378673,3378988,3378144,3378673,3378988,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378673,3378673,3378673,3378673,3378673,3378673,3378673</t>
+          <t>3378136,3378019,3378242,3378019,3378668,3378253,3378326,3378136,3378019,3378242,3378019,3378668,3378253,3378136,3378019,3378242,3378019,3378668,3378253,3378136,3378091,3378242,3378091,3378668,3378325,3378136,3378091,3378242,3378091,3378668,3378325,3378136,3378091,3378242,3378091,3378668,3378325,3378136,3378091,3378466,3378091,3378668,3378645,3378136,3378099,3378466,3378099,3378668,3378645,3378136,3378099,3378466,3378099,3378868,3378645,3378136,3378099,3378466,3378099,3378868,3378693,3378136,3378107,3378466,3378107,3378868,3378693,3378136,3378107,3378466,3378107,3378868,3378693,3378136,3378107,3378786,3378107,3378868,3378709,3378136,3378107,3378786,3378107,3378868,3378709,3378136,3378115,3378786,3378115,3378868,3378709,3378136,3378115,3378786,3378115,3378988,3378136,3378115,3378786,3378115,3378988,3378136,3378115,3378786,3378115,3378988,3378144,3378673,3378988,3378144,3378673,3378988,3378144,3378673,3378988,3378144,3378673,3378988,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378673,3378673,3378673,3378673,3378673,3378673,3378673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L7 W20/25; N=151; EHP=16883.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x17,fast:30x6,heavy:31x3,elite:40x1,heavy:40x3,fast:58x6,heavy:80x3,medium:83x8,swarm:84x42,heavy:86x3,heavy:88x3,fast:98x6,medium:108x7,medium:123x7</t>
+          <t>L7 W20/25; N=151; EHP=33609.322831; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,elite:40x1,fast:30x6,fast:58x6,fast:98x6,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x8,medium:108x7,medium:123x7,normal:17x18,normal:18x17,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017133,10017141,10017135,10048530,10017140,10017136,10017133,10017141,10017135,10048530,10017140,10017136,10017133,10017141,10017135,10048530,10017140,10017136,10017133,10017141,10017135,10048530,10017140,10017137,10017133,10017141,10017135,10017130,10017140,10017137,10017133,10017141,10017135,10017130,10017140,10017137,10017133,10017141,10017138,10017130,10017140,10017139,10017133,10017141,10017138,10017130,10017145,10017139,10017133,10017141,10017138,10048531,10017145,10017139,10017133,10017141,10017138,10048531,10017145,10017142,10017133,10017141,10017138,10048531,10017145,10017142,10017133,10017141,10017138,10048531,10017145,10017142,10017133,10017141,10017144,10017131,10017145,10017143,10017133,10017141,10017144,10017131,10017145,10017143,10017133,10017141,10017144,10017131,10017145,10017143,10017133,10017141,10017144,10017132,10017146,10017133,10017141,10017144,10017132,10017146,10017133,10017141,10017144,10017132,10017146,10017133,10017141,10017132,10017146,10017134,10017141,10017146,10017134,10017141,10017146,10017134,10017141,10017146,10017134,10017141,10017146,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017141,10017141,10017141,10017141</t>
+          <t>10017133,10048530,10017135,10048530,10017140,10017136,10017133,10048530,10017135,10048530,10017140,10017136,10017133,10048530,10017135,10048530,10017140,10017136,10017133,10048530,10017135,10048530,10017140,10017137,10017133,10017130,10017135,10017130,10017140,10017137,10017133,10017130,10017135,10017130,10017140,10017137,10017133,10017130,10017138,10017130,10017140,10017139,10017133,10017130,10017138,10017130,10017145,10017139,10017133,10048531,10017138,10048531,10017145,10017139,10017133,10048531,10017138,10048531,10017145,10017142,10017133,10048531,10017138,10048531,10017145,10017142,10017133,10048531,10017138,10048531,10017145,10017142,10017133,10017131,10017144,10017131,10017145,10017143,10017133,10017131,10017144,10017131,10017145,10017143,10017133,10017131,10017144,10017131,10017145,10017143,10017133,10017132,10017144,10017132,10017146,10017133,10017132,10017144,10017132,10017146,10017133,10017132,10017144,10017132,10017146,10017133,10017132,10017132,10017146,10017134,10017141,10017146,10017134,10017141,10017146,10017134,10017141,10017146,10017134,10017141,10017146,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017134,10017141,10017141,10017141,10017141,10017141</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L7 W21/25; N=157; EHP=17221.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x20,fast:30x6,heavy:31x3,heavy:40x3,fast:58x6,heavy:80x3,medium:83x7,swarm:84x43,heavy:86x3,heavy:88x3,fast:98x6,medium:108x8,medium:123x8</t>
+          <t>L7 W21/25; N=157; EHP=34298.341703; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x6,fast:58x6,fast:98x6,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x7,medium:108x8,medium:123x8,normal:17x19,normal:18x20,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017150,10017158,10017152,10048532,10017157,10017153,10017150,10017158,10017152,10048532,10017157,10017153,10017150,10017158,10017152,10048532,10017157,10017153,10017150,10017158,10017152,10048532,10017157,10017154,10017150,10017158,10017152,10017147,10017157,10017154,10017150,10017158,10017152,10017147,10017157,10017154,10017150,10017158,10017155,10017147,10017157,10017154,10017150,10017158,10017155,10017147,10017157,10017156,10017150,10017158,10017155,10048533,10017162,10017156,10017150,10017158,10017155,10048533,10017162,10017156,10017150,10017158,10017155,10048533,10017162,10017159,10017150,10017158,10017155,10048533,10017162,10017159,10017150,10017158,10017155,10017148,10017162,10017159,10017150,10017158,10017161,10017148,10017162,10017160,10017150,10017158,10017161,10017148,10017162,10017160,10017150,10017158,10017161,10017148,10017162,10017160,10017150,10017158,10017161,10017149,10017163,10017150,10017158,10017161,10017149,10017163,10017150,10017158,10017161,10017149,10017163,10017150,10017158,10017149,10017163,10017151,10017158,10017163,10017151,10017158,10017163,10017151,10017158,10017163,10017151,10017158,10017163,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017158,10017158,10017158,10017158,10017158,10017158</t>
+          <t>10017150,10048532,10017152,10048532,10017157,10017153,10017150,10048532,10017152,10048532,10017157,10017153,10017150,10048532,10017152,10048532,10017157,10017153,10017150,10048532,10017152,10048532,10017157,10017154,10017150,10017147,10017152,10017147,10017157,10017154,10017150,10017147,10017152,10017147,10017157,10017154,10017150,10017147,10017155,10017147,10017157,10017154,10017150,10017147,10017155,10017147,10017157,10017156,10017150,10048533,10017155,10048533,10017162,10017156,10017150,10048533,10017155,10048533,10017162,10017156,10017150,10048533,10017155,10048533,10017162,10017159,10017150,10048533,10017155,10048533,10017162,10017159,10017150,10017148,10017155,10017148,10017162,10017159,10017150,10017148,10017161,10017148,10017162,10017160,10017150,10017148,10017161,10017148,10017162,10017160,10017150,10017148,10017161,10017148,10017162,10017160,10017150,10017149,10017161,10017149,10017163,10017150,10017149,10017161,10017149,10017163,10017150,10017149,10017161,10017149,10017163,10017150,10017149,10017149,10017163,10017151,10017158,10017163,10017151,10017158,10017163,10017151,10017158,10017163,10017151,10017158,10017163,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017151,10017158,10017158,10017158,10017158,10017158,10017158,10017158</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L7 W22/25; N=163; EHP=17566.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x19,fast:30x6,heavy:31x3,heavy:40x4,fast:58x7,heavy:80x3,medium:83x8,swarm:84x45,heavy:86x3,heavy:88x3,fast:98x6,medium:108x8,medium:123x8</t>
+          <t>L7 W22/25; N=163; EHP=34990.401269; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x6,fast:58x7,fast:98x6,heavy:31x3,heavy:40x4,heavy:80x3,heavy:86x3,heavy:88x3,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017167,10017175,10017169,10048534,10017174,10017170,10017167,10017175,10017169,10048534,10017174,10017170,10017167,10017175,10017169,10048534,10017174,10017170,10017167,10017175,10017169,10048534,10017174,10017171,10017167,10017175,10017169,10017164,10017174,10017171,10017167,10017175,10017169,10017164,10017174,10017171,10017167,10017175,10017169,10017164,10017174,10017173,10017167,10017175,10017172,10017164,10017174,10017173,10017167,10017175,10017172,10048535,10017174,10017173,10017167,10017175,10017172,10048535,10017179,10017176,10017167,10017175,10017172,10048535,10017179,10017176,10017167,10017175,10017172,10048535,10017179,10017176,10017167,10017175,10017172,10017165,10017179,10017177,10017167,10017175,10017178,10017165,10017179,10017177,10017167,10017175,10017178,10017165,10017179,10017177,10017167,10017175,10017178,10017165,10017179,10017177,10017167,10017175,10017178,10017166,10017179,10017167,10017175,10017178,10017166,10017180,10017167,10017175,10017178,10017166,10017180,10017167,10017175,10017178,10017166,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017175,10017175,10017175,10017175,10017175,10017175</t>
+          <t>10017167,10048534,10017169,10048534,10017174,10017170,10017167,10048534,10017169,10048534,10017174,10017170,10017167,10048534,10017169,10048534,10017174,10017170,10017167,10048534,10017169,10048534,10017174,10017171,10017167,10017164,10017169,10017164,10017174,10017171,10017167,10017164,10017169,10017164,10017174,10017171,10017167,10017164,10017169,10017164,10017174,10017173,10017167,10017164,10017172,10017164,10017174,10017173,10017167,10048535,10017172,10048535,10017174,10017173,10017167,10048535,10017172,10048535,10017179,10017176,10017167,10048535,10017172,10048535,10017179,10017176,10017167,10048535,10017172,10048535,10017179,10017176,10017167,10017165,10017172,10017165,10017179,10017177,10017167,10017165,10017178,10017165,10017179,10017177,10017167,10017165,10017178,10017165,10017179,10017177,10017167,10017165,10017178,10017165,10017179,10017177,10017167,10017166,10017178,10017166,10017179,10017167,10017166,10017178,10017166,10017180,10017167,10017166,10017178,10017166,10017180,10017167,10017166,10017178,10017166,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017180,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017168,10017175,10017175,10017175,10017175,10017175,10017175,10017175</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L7 W23/25; N=169; EHP=17918.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x7,heavy:31x3,heavy:40x3,fast:58x6,heavy:80x3,medium:83x9,swarm:84x47,heavy:86x3,heavy:88x4,fast:98x7,medium:108x8,medium:123x8</t>
+          <t>L7 W23/25; N=169; EHP=35677.661643; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x7,fast:58x6,fast:98x7,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x4,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017184,10017192,10017186,10048536,10017191,10017187,10017184,10017192,10017186,10048536,10017191,10017187,10017184,10017192,10017186,10048536,10017191,10017187,10017184,10017192,10017186,10048536,10017191,10017188,10017184,10017192,10017186,10048536,10017191,10017188,10017184,10017192,10017186,10017181,10017191,10017188,10017184,10017192,10017186,10017181,10017191,10017190,10017184,10017192,10017189,10017181,10017191,10017190,10017184,10017192,10017189,10017181,10017196,10017190,10017184,10017192,10017189,10048537,10017196,10017190,10017184,10017192,10017189,10048537,10017196,10017193,10017184,10017192,10017189,10048537,10017196,10017193,10017184,10017192,10017189,10048537,10017196,10017193,10017184,10017192,10017189,10017182,10017196,10017193,10017184,10017192,10017195,10017182,10017196,10017194,10017184,10017192,10017195,10017182,10017196,10017194,10017184,10017192,10017195,10017182,10017196,10017194,10017184,10017192,10017195,10017183,10017197,10017184,10017192,10017195,10017183,10017197,10017184,10017192,10017195,10017183,10017197,10017184,10017192,10017195,10017183,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017192,10017192,10017192,10017192,10017192,10017192,10017192,10017192</t>
+          <t>10017184,10048536,10017186,10048536,10017191,10017187,10017184,10048536,10017186,10048536,10017191,10017187,10017184,10048536,10017186,10048536,10017191,10017187,10017184,10048536,10017186,10048536,10017191,10017188,10017184,10048536,10017186,10048536,10017191,10017188,10017184,10017181,10017186,10017181,10017191,10017188,10017184,10017181,10017186,10017181,10017191,10017190,10017184,10017181,10017189,10017181,10017191,10017190,10017184,10017181,10017189,10017181,10017196,10017190,10017184,10048537,10017189,10048537,10017196,10017190,10017184,10048537,10017189,10048537,10017196,10017193,10017184,10048537,10017189,10048537,10017196,10017193,10017184,10048537,10017189,10048537,10017196,10017193,10017184,10017182,10017189,10017182,10017196,10017193,10017184,10017182,10017195,10017182,10017196,10017194,10017184,10017182,10017195,10017182,10017196,10017194,10017184,10017182,10017195,10017182,10017196,10017194,10017184,10017183,10017195,10017183,10017197,10017184,10017183,10017195,10017183,10017197,10017184,10017183,10017195,10017183,10017197,10017184,10017183,10017195,10017183,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017197,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017185,10017192,10017192,10017192,10017192,10017192,10017192,10017192,10017192,10017192</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L7 W24/25; N=175; EHP=19186.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x7,heavy:31x3,heavy:40x3,fast:58x7,heavy:80x4,medium:83x8,swarm:84x49,heavy:86x4,heavy:88x3,fast:98x7,medium:108x9,medium:123x9</t>
+          <t>L7 W24/25; N=175; EHP=38207.822522; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x7,fast:58x7,fast:98x7,heavy:31x3,heavy:40x3,heavy:80x4,heavy:86x4,heavy:88x3,medium:83x8,medium:108x9,medium:123x9,normal:17x21,normal:18x20,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017201,10017209,10017203,10048538,10017208,10017204,10017214,10017201,10017209,10017203,10048538,10017208,10017204,10017201,10017209,10017203,10048538,10017208,10017204,10017201,10017209,10017203,10048538,10017208,10017204,10017201,10017209,10017203,10017198,10017208,10017205,10017201,10017209,10017203,10017198,10017208,10017205,10017201,10017209,10017203,10017198,10017208,10017205,10017201,10017209,10017206,10017198,10017208,10017205,10017201,10017209,10017206,10017198,10017208,10017207,10017201,10017209,10017206,10048539,10017213,10017207,10017201,10017209,10017206,10048539,10017213,10017207,10017201,10017209,10017206,10048539,10017213,10017210,10017201,10017209,10017206,10048539,10017213,10017210,10017201,10017209,10017206,10017199,10017213,10017210,10017201,10017209,10017212,10017199,10017213,10017210,10017201,10017209,10017212,10017199,10017213,10017211,10017201,10017209,10017212,10017199,10017213,10017211,10017201,10017209,10017212,10017199,10017213,10017211,10017201,10017209,10017212,10017200,10017215,10017201,10017209,10017212,10017200,10017215,10017201,10017209,10017212,10017200,10017215,10017202,10017209,10017200,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017209,10017209,10017209,10017209,10017209,10017209,10017209,10017209</t>
+          <t>10017201,10048538,10017203,10048538,10017208,10017204,10017214,10017201,10048538,10017203,10048538,10017208,10017204,10017201,10048538,10017203,10048538,10017208,10017204,10017201,10048538,10017203,10048538,10017208,10017204,10017201,10017198,10017203,10017198,10017208,10017205,10017201,10017198,10017203,10017198,10017208,10017205,10017201,10017198,10017203,10017198,10017208,10017205,10017201,10017198,10017206,10017198,10017208,10017205,10017201,10017198,10017206,10017198,10017208,10017207,10017201,10048539,10017206,10048539,10017213,10017207,10017201,10048539,10017206,10048539,10017213,10017207,10017201,10048539,10017206,10048539,10017213,10017210,10017201,10048539,10017206,10048539,10017213,10017210,10017201,10017199,10017206,10017199,10017213,10017210,10017201,10017199,10017212,10017199,10017213,10017210,10017201,10017199,10017212,10017199,10017213,10017211,10017201,10017199,10017212,10017199,10017213,10017211,10017201,10017199,10017212,10017199,10017213,10017211,10017201,10017200,10017212,10017200,10017215,10017201,10017200,10017212,10017200,10017215,10017201,10017200,10017212,10017200,10017215,10017202,10017200,10017200,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017215,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017202,10017209,10017209,10017209,10017209,10017209,10017209,10017209,10017209,10017209</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L7 W25/25; N=181; EHP=38300.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x21,fast:30x7,heavy:31x4,heavy:40x4,fast:58x7,heavy:80x3,medium:83x9,swarm:84x50,heavy:86x4,heavy:88x3,fast:98x7,medium:108x9,elite:123x1,medium:123x9</t>
+          <t>L7 W25/25; N=181; EHP=76262.554846; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x7,fast:58x7,fast:98x7,heavy:31x4,heavy:40x4,heavy:80x3,heavy:86x4,heavy:88x3,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L07/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L07/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>268</v>
+        <v>330</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>247</v>
+        <v>340</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>191</v>
+        <v>290</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>142</v>
+        <v>270</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
